--- a/infor-beta/templates/INFOR Precedents Template.xlsx
+++ b/infor-beta/templates/INFOR Precedents Template.xlsx
@@ -8,7 +8,13 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Precedents" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="infor_prec_group1_block" localSheetId="0">'Precedents'!$B$8:$AI$13</definedName>
+    <definedName name="infor_prec_group1_label" localSheetId="0">'Precedents'!$E$7</definedName>
+    <definedName name="infor_prec_group2_block" localSheetId="0">'Precedents'!$B$17:$AI$22</definedName>
+    <definedName name="infor_prec_group2_label" localSheetId="0">'Precedents'!$E$16</definedName>
+    <definedName name="infor_prec_output_ccy" localSheetId="0">'Precedents'!$C$2</definedName>
+  </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
